--- a/listas/output/Lista Papu.xlsx
+++ b/listas/output/Lista Papu.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="314">
   <si>
     <t>VENTANAS HERRERO</t>
   </si>
@@ -7624,8 +7624,8 @@
       <c r="A22" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>169</v>
+      <c r="B22" s="4">
+        <v>289192</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>169</v>

--- a/listas/output/Lista Papu.xlsx
+++ b/listas/output/Lista Papu.xlsx
@@ -2056,16 +2056,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="4">
-        <v>28904</v>
+        <v>25209</v>
       </c>
       <c r="C6" s="4">
-        <v>36083</v>
+        <v>32388</v>
       </c>
       <c r="D6" s="4">
         <v>9659</v>
       </c>
       <c r="E6" s="4">
-        <v>37575</v>
+        <v>32772</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
